--- a/학평.xlsx
+++ b/학평.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ahn\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D50A5038-7003-4BA0-B874-7ADA9BC90E18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86DDF99E-CC8A-4C13-AFC2-883F8C5B0F44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="36045" yWindow="0" windowWidth="21600" windowHeight="11295" xr2:uid="{94A5CD0E-065E-4B35-B399-E04F27AE39B2}"/>
+    <workbookView xWindow="36000" yWindow="0" windowWidth="21600" windowHeight="11295" xr2:uid="{94A5CD0E-065E-4B35-B399-E04F27AE39B2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -78,10 +78,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>1-7</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>국어</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -95,6 +91,10 @@
   </si>
   <si>
     <t>탐구(교대)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>107</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -230,6 +230,24 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="1" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -243,24 +261,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -601,144 +601,144 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="11" t="s">
         <v>6</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
-      <c r="D2" s="10" t="s">
-        <v>12</v>
+      <c r="D2" s="5" t="s">
+        <v>16</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
     </row>
     <row r="3" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="6"/>
+      <c r="A3" s="12"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
-      <c r="D3" s="12" t="s">
-        <v>13</v>
+      <c r="D3" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="11" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
-      <c r="D4" s="13"/>
+      <c r="D4" s="8"/>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
     </row>
     <row r="5" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="6"/>
+      <c r="A5" s="12"/>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
-      <c r="D5" s="11"/>
+      <c r="D5" s="6"/>
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="11" t="s">
         <v>8</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
-      <c r="D6" s="10" t="s">
-        <v>12</v>
+      <c r="D6" s="5" t="s">
+        <v>16</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
     </row>
     <row r="7" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="6"/>
+      <c r="A7" s="12"/>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
-      <c r="D7" s="12" t="s">
-        <v>14</v>
+      <c r="D7" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="11" t="s">
         <v>9</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
-      <c r="D8" s="10" t="s">
-        <v>12</v>
+      <c r="D8" s="5" t="s">
+        <v>16</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
     </row>
     <row r="9" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="6"/>
+      <c r="A9" s="12"/>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
-      <c r="D9" s="12" t="s">
-        <v>15</v>
+      <c r="D9" s="7" t="s">
+        <v>14</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="11" t="s">
         <v>10</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
-      <c r="D10" s="10"/>
+      <c r="D10" s="5"/>
       <c r="E10" s="2"/>
-      <c r="F10" s="7"/>
+      <c r="F10" s="13"/>
     </row>
     <row r="11" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="6"/>
+      <c r="A11" s="12"/>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
-      <c r="D11" s="11"/>
+      <c r="D11" s="6"/>
       <c r="E11" s="3"/>
-      <c r="F11" s="8"/>
+      <c r="F11" s="14"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="11" t="s">
         <v>11</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
-      <c r="D12" s="14" t="s">
-        <v>12</v>
+      <c r="D12" s="9" t="s">
+        <v>16</v>
       </c>
       <c r="E12" s="2"/>
-      <c r="F12" s="7"/>
+      <c r="F12" s="13"/>
     </row>
     <row r="13" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="6"/>
+      <c r="A13" s="12"/>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
-      <c r="D13" s="15" t="s">
-        <v>16</v>
+      <c r="D13" s="10" t="s">
+        <v>15</v>
       </c>
       <c r="E13" s="3"/>
-      <c r="F13" s="8"/>
+      <c r="F13" s="14"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="5"/>
+      <c r="A14" s="11"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
-      <c r="D14" s="10"/>
+      <c r="D14" s="5"/>
       <c r="E14" s="2"/>
-      <c r="F14" s="9"/>
+      <c r="F14" s="15"/>
     </row>
     <row r="15" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="6"/>
+      <c r="A15" s="12"/>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
-      <c r="D15" s="11"/>
+      <c r="D15" s="6"/>
       <c r="E15" s="3"/>
-      <c r="F15" s="8"/>
+      <c r="F15" s="14"/>
     </row>
     <row r="16" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="1"/>

--- a/학평.xlsx
+++ b/학평.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ahn\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86DDF99E-CC8A-4C13-AFC2-883F8C5B0F44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E49EC694-5A92-4B55-B0D6-01419D6836E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="36000" yWindow="0" windowWidth="21600" windowHeight="11295" xr2:uid="{94A5CD0E-065E-4B35-B399-E04F27AE39B2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{94A5CD0E-065E-4B35-B399-E04F27AE39B2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -604,13 +604,17 @@
       <c r="A2" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="2"/>
+      <c r="B2" s="2">
+        <v>303</v>
+      </c>
       <c r="C2" s="2"/>
       <c r="D2" s="5" t="s">
         <v>16</v>
       </c>
       <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
+      <c r="F2" s="2">
+        <v>203</v>
+      </c>
     </row>
     <row r="3" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="12"/>
@@ -630,7 +634,9 @@
       <c r="C4" s="2"/>
       <c r="D4" s="8"/>
       <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
+      <c r="F4" s="2">
+        <v>203</v>
+      </c>
     </row>
     <row r="5" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="12"/>
@@ -644,7 +650,9 @@
       <c r="A6" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="2"/>
+      <c r="B6" s="2">
+        <v>303</v>
+      </c>
       <c r="C6" s="2"/>
       <c r="D6" s="5" t="s">
         <v>16</v>
@@ -666,13 +674,17 @@
       <c r="A8" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="2"/>
+      <c r="B8" s="2">
+        <v>303</v>
+      </c>
       <c r="C8" s="2"/>
       <c r="D8" s="5" t="s">
         <v>16</v>
       </c>
       <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
+      <c r="F8" s="2">
+        <v>203</v>
+      </c>
     </row>
     <row r="9" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="12"/>
@@ -692,7 +704,9 @@
       <c r="C10" s="2"/>
       <c r="D10" s="5"/>
       <c r="E10" s="2"/>
-      <c r="F10" s="13"/>
+      <c r="F10" s="13">
+        <v>203</v>
+      </c>
     </row>
     <row r="11" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="12"/>
@@ -706,13 +720,17 @@
       <c r="A12" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="2"/>
+      <c r="B12" s="2">
+        <v>303</v>
+      </c>
       <c r="C12" s="2"/>
       <c r="D12" s="9" t="s">
         <v>16</v>
       </c>
       <c r="E12" s="2"/>
-      <c r="F12" s="13"/>
+      <c r="F12" s="13">
+        <v>203</v>
+      </c>
     </row>
     <row r="13" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="12"/>

--- a/학평.xlsx
+++ b/학평.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ahn\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ahn\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E49EC694-5A92-4B55-B0D6-01419D6836E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C8E93AC-BCE0-4B3E-ABAC-4D7F44343CD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{94A5CD0E-065E-4B35-B399-E04F27AE39B2}"/>
   </bookViews>
@@ -604,17 +604,13 @@
       <c r="A2" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="2">
-        <v>303</v>
-      </c>
+      <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="5" t="s">
         <v>16</v>
       </c>
       <c r="E2" s="2"/>
-      <c r="F2" s="2">
-        <v>203</v>
-      </c>
+      <c r="F2" s="2"/>
     </row>
     <row r="3" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="12"/>
@@ -630,9 +626,13 @@
       <c r="A4" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="2"/>
+      <c r="B4" s="2">
+        <v>303</v>
+      </c>
       <c r="C4" s="2"/>
-      <c r="D4" s="8"/>
+      <c r="D4" s="8" t="s">
+        <v>16</v>
+      </c>
       <c r="E4" s="2"/>
       <c r="F4" s="2">
         <v>203</v>
@@ -642,7 +642,9 @@
       <c r="A5" s="12"/>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
-      <c r="D5" s="6"/>
+      <c r="D5" s="7" t="s">
+        <v>13</v>
+      </c>
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
     </row>
@@ -654,19 +656,17 @@
         <v>303</v>
       </c>
       <c r="C6" s="2"/>
-      <c r="D6" s="5" t="s">
-        <v>16</v>
-      </c>
+      <c r="D6" s="5"/>
       <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
+      <c r="F6" s="2">
+        <v>203</v>
+      </c>
     </row>
     <row r="7" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="12"/>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
-      <c r="D7" s="7" t="s">
-        <v>13</v>
-      </c>
+      <c r="D7" s="7"/>
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
     </row>
@@ -674,17 +674,13 @@
       <c r="A8" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="2">
-        <v>303</v>
-      </c>
+      <c r="B8" s="2"/>
       <c r="C8" s="2"/>
       <c r="D8" s="5" t="s">
         <v>16</v>
       </c>
       <c r="E8" s="2"/>
-      <c r="F8" s="2">
-        <v>203</v>
-      </c>
+      <c r="F8" s="2"/>
     </row>
     <row r="9" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="12"/>
@@ -704,9 +700,7 @@
       <c r="C10" s="2"/>
       <c r="D10" s="5"/>
       <c r="E10" s="2"/>
-      <c r="F10" s="13">
-        <v>203</v>
-      </c>
+      <c r="F10" s="13"/>
     </row>
     <row r="11" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="12"/>
